--- a/glossary.xlsx
+++ b/glossary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105215B6-4183-FA44-891E-21F40F93D067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C96E461-EA20-0946-ACA9-9B5A077DACDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{FD61D8A1-D7A7-6B4D-AB92-59721C5EF8F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="336">
   <si>
     <t>Topic</t>
   </si>
@@ -1134,6 +1134,15 @@
   </si>
   <si>
     <t>Nema 1-15, Nema 5-15</t>
+  </si>
+  <si>
+    <t>MIB</t>
+  </si>
+  <si>
+    <t>Move In Black</t>
+  </si>
+  <si>
+    <t>A programming feature on consoles like GrandMA3 that permits the console to look ahead to future moving fixture locations and pre-position movers while they are at dimmer=0 (ie Black) to the predicted future location.</t>
   </si>
 </sst>
 </file>
@@ -1214,8 +1223,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:E159" totalsRowShown="0" dataDxfId="5">
-  <autoFilter ref="A1:E159" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}" name="Table1" displayName="Table1" ref="A1:E161" totalsRowShown="0" dataDxfId="5">
+  <autoFilter ref="A1:E161" xr:uid="{314A4941-A8BA-2346-8EA0-5892B4F1C3B7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E159">
     <sortCondition ref="B1:B159"/>
   </sortState>
@@ -1527,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327B4C12-DB51-F04E-97D5-67343BD74C6D}">
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -3979,6 +3988,38 @@
         <v>43</v>
       </c>
     </row>
+    <row r="160" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E161" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
